--- a/WebPortal/TempFiles/Andrew.xlsx
+++ b/WebPortal/TempFiles/Andrew.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ntj\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\icg\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CD1397DC-BD1E-46AD-997B-77803BD844F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A55A08D-BFF3-4D2B-BD5E-B7560EB0D6B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19080" yWindow="-2130" windowWidth="19440" windowHeight="15000" xr2:uid="{62B37C17-0668-4F04-A2FC-02DFCE0274FC}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{62B37C17-0668-4F04-A2FC-02DFCE0274FC}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="14">
   <si>
     <t>LoanNo</t>
   </si>
@@ -795,810 +795,314 @@
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="B11" s="3">
-        <v>177038</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="E11" s="5">
-        <v>46209</v>
-      </c>
-      <c r="F11" s="5">
-        <v>46209</v>
-      </c>
-      <c r="G11" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="H11" s="4" t="s">
-        <v>10</v>
-      </c>
+      <c r="A11" s="6"/>
+      <c r="B11" s="3"/>
+      <c r="C11" s="3"/>
+      <c r="D11" s="4"/>
+      <c r="E11" s="5"/>
+      <c r="F11" s="5"/>
+      <c r="G11" s="4"/>
+      <c r="H11" s="4"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="B12" s="3">
-        <v>177053</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="E12" s="5">
-        <v>46209</v>
-      </c>
-      <c r="F12" s="5">
-        <v>46209</v>
-      </c>
-      <c r="G12" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="H12" s="4" t="s">
-        <v>10</v>
-      </c>
+      <c r="A12" s="6"/>
+      <c r="B12" s="3"/>
+      <c r="C12" s="3"/>
+      <c r="D12" s="4"/>
+      <c r="E12" s="5"/>
+      <c r="F12" s="5"/>
+      <c r="G12" s="4"/>
+      <c r="H12" s="4"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A13" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="B13" s="3">
-        <v>177058</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D13" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="E13" s="5">
-        <v>46209</v>
-      </c>
-      <c r="F13" s="5">
-        <v>46209</v>
-      </c>
-      <c r="G13" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="H13" s="4" t="s">
-        <v>10</v>
-      </c>
+      <c r="A13" s="6"/>
+      <c r="B13" s="3"/>
+      <c r="C13" s="3"/>
+      <c r="D13" s="4"/>
+      <c r="E13" s="5"/>
+      <c r="F13" s="5"/>
+      <c r="G13" s="4"/>
+      <c r="H13" s="4"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="B14" s="3">
-        <v>177059</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D14" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="E14" s="5">
-        <v>46209</v>
-      </c>
-      <c r="F14" s="5">
-        <v>46209</v>
-      </c>
-      <c r="G14" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="H14" s="4" t="s">
-        <v>10</v>
-      </c>
+      <c r="A14" s="6"/>
+      <c r="B14" s="3"/>
+      <c r="C14" s="3"/>
+      <c r="D14" s="4"/>
+      <c r="E14" s="5"/>
+      <c r="F14" s="5"/>
+      <c r="G14" s="4"/>
+      <c r="H14" s="4"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A15" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="B15" s="3">
-        <v>177062</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D15" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="E15" s="5">
-        <v>46209</v>
-      </c>
-      <c r="F15" s="5">
-        <v>46209</v>
-      </c>
-      <c r="G15" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="H15" s="4" t="s">
-        <v>10</v>
-      </c>
+      <c r="A15" s="6"/>
+      <c r="B15" s="3"/>
+      <c r="C15" s="3"/>
+      <c r="D15" s="4"/>
+      <c r="E15" s="5"/>
+      <c r="F15" s="5"/>
+      <c r="G15" s="4"/>
+      <c r="H15" s="4"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A16" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="B16" s="3">
-        <v>177064</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D16" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="E16" s="5">
-        <v>46209</v>
-      </c>
-      <c r="F16" s="5">
-        <v>46209</v>
-      </c>
-      <c r="G16" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="H16" s="4" t="s">
-        <v>10</v>
-      </c>
+      <c r="A16" s="6"/>
+      <c r="B16" s="3"/>
+      <c r="C16" s="3"/>
+      <c r="D16" s="4"/>
+      <c r="E16" s="5"/>
+      <c r="F16" s="5"/>
+      <c r="G16" s="4"/>
+      <c r="H16" s="4"/>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A17" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="B17" s="3">
-        <v>177065</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D17" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="E17" s="5">
-        <v>46209</v>
-      </c>
-      <c r="F17" s="5">
-        <v>46209</v>
-      </c>
-      <c r="G17" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="H17" s="4" t="s">
-        <v>10</v>
-      </c>
+      <c r="A17" s="6"/>
+      <c r="B17" s="3"/>
+      <c r="C17" s="3"/>
+      <c r="D17" s="4"/>
+      <c r="E17" s="5"/>
+      <c r="F17" s="5"/>
+      <c r="G17" s="4"/>
+      <c r="H17" s="4"/>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A18" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="B18" s="3">
-        <v>177066</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D18" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="E18" s="5">
-        <v>46209</v>
-      </c>
-      <c r="F18" s="5">
-        <v>46209</v>
-      </c>
-      <c r="G18" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="H18" s="4" t="s">
-        <v>10</v>
-      </c>
+      <c r="A18" s="6"/>
+      <c r="B18" s="3"/>
+      <c r="C18" s="3"/>
+      <c r="D18" s="4"/>
+      <c r="E18" s="5"/>
+      <c r="F18" s="5"/>
+      <c r="G18" s="4"/>
+      <c r="H18" s="4"/>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A19" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="B19" s="3">
-        <v>177069</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D19" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="E19" s="5">
-        <v>46209</v>
-      </c>
-      <c r="F19" s="5">
-        <v>46209</v>
-      </c>
-      <c r="G19" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="H19" s="4" t="s">
-        <v>10</v>
-      </c>
+      <c r="A19" s="6"/>
+      <c r="B19" s="3"/>
+      <c r="C19" s="3"/>
+      <c r="D19" s="4"/>
+      <c r="E19" s="5"/>
+      <c r="F19" s="5"/>
+      <c r="G19" s="4"/>
+      <c r="H19" s="4"/>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A20" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="B20" s="3">
-        <v>177070</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D20" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="E20" s="5">
-        <v>46209</v>
-      </c>
-      <c r="F20" s="5">
-        <v>46209</v>
-      </c>
-      <c r="G20" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="H20" s="4" t="s">
-        <v>10</v>
-      </c>
+      <c r="A20" s="6"/>
+      <c r="B20" s="3"/>
+      <c r="C20" s="3"/>
+      <c r="D20" s="4"/>
+      <c r="E20" s="5"/>
+      <c r="F20" s="5"/>
+      <c r="G20" s="4"/>
+      <c r="H20" s="4"/>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A21" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="B21" s="3">
-        <v>177072</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D21" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="E21" s="5">
-        <v>46209</v>
-      </c>
-      <c r="F21" s="5">
-        <v>46209</v>
-      </c>
-      <c r="G21" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="H21" s="4" t="s">
-        <v>10</v>
-      </c>
+      <c r="A21" s="6"/>
+      <c r="B21" s="3"/>
+      <c r="C21" s="3"/>
+      <c r="D21" s="4"/>
+      <c r="E21" s="5"/>
+      <c r="F21" s="5"/>
+      <c r="G21" s="4"/>
+      <c r="H21" s="4"/>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A22" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="B22" s="3">
-        <v>173143</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D22" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="E22" s="5">
-        <v>46209</v>
-      </c>
-      <c r="F22" s="5">
-        <v>46209</v>
-      </c>
-      <c r="G22" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="H22" s="4" t="s">
-        <v>10</v>
-      </c>
+      <c r="A22" s="6"/>
+      <c r="B22" s="3"/>
+      <c r="C22" s="3"/>
+      <c r="D22" s="4"/>
+      <c r="E22" s="5"/>
+      <c r="F22" s="5"/>
+      <c r="G22" s="4"/>
+      <c r="H22" s="4"/>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A23" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="B23" s="3">
-        <v>173315</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D23" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="E23" s="5">
-        <v>46209</v>
-      </c>
-      <c r="F23" s="5">
-        <v>46209</v>
-      </c>
-      <c r="G23" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="H23" s="4" t="s">
-        <v>10</v>
-      </c>
+      <c r="A23" s="6"/>
+      <c r="B23" s="3"/>
+      <c r="C23" s="3"/>
+      <c r="D23" s="4"/>
+      <c r="E23" s="5"/>
+      <c r="F23" s="5"/>
+      <c r="G23" s="4"/>
+      <c r="H23" s="4"/>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A24" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="B24" s="3">
-        <v>173351</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D24" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="E24" s="5">
-        <v>46209</v>
-      </c>
-      <c r="F24" s="5">
-        <v>46209</v>
-      </c>
-      <c r="G24" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="H24" s="4" t="s">
-        <v>10</v>
-      </c>
+      <c r="A24" s="6"/>
+      <c r="B24" s="3"/>
+      <c r="C24" s="3"/>
+      <c r="D24" s="4"/>
+      <c r="E24" s="5"/>
+      <c r="F24" s="5"/>
+      <c r="G24" s="4"/>
+      <c r="H24" s="4"/>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A25" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="B25" s="3">
-        <v>177007</v>
-      </c>
-      <c r="C25" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D25" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="E25" s="5">
-        <v>46209</v>
-      </c>
-      <c r="F25" s="5">
-        <v>46209</v>
-      </c>
-      <c r="G25" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="H25" s="4" t="s">
-        <v>10</v>
-      </c>
+      <c r="A25" s="6"/>
+      <c r="B25" s="3"/>
+      <c r="C25" s="3"/>
+      <c r="D25" s="4"/>
+      <c r="E25" s="5"/>
+      <c r="F25" s="5"/>
+      <c r="G25" s="4"/>
+      <c r="H25" s="4"/>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A26" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="B26" s="3">
-        <v>177037</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D26" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="E26" s="5">
-        <v>46209</v>
-      </c>
-      <c r="F26" s="5">
-        <v>46209</v>
-      </c>
-      <c r="G26" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="H26" s="4" t="s">
-        <v>10</v>
-      </c>
+      <c r="A26" s="6"/>
+      <c r="B26" s="3"/>
+      <c r="C26" s="3"/>
+      <c r="D26" s="4"/>
+      <c r="E26" s="5"/>
+      <c r="F26" s="5"/>
+      <c r="G26" s="4"/>
+      <c r="H26" s="4"/>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A27" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="B27" s="3">
-        <v>177047</v>
-      </c>
-      <c r="C27" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D27" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="E27" s="5">
-        <v>46209</v>
-      </c>
-      <c r="F27" s="5">
-        <v>46209</v>
-      </c>
-      <c r="G27" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="H27" s="4" t="s">
-        <v>10</v>
-      </c>
+      <c r="A27" s="6"/>
+      <c r="B27" s="3"/>
+      <c r="C27" s="3"/>
+      <c r="D27" s="4"/>
+      <c r="E27" s="5"/>
+      <c r="F27" s="5"/>
+      <c r="G27" s="4"/>
+      <c r="H27" s="4"/>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A28" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="B28" s="3">
-        <v>173328</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D28" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="E28" s="5">
-        <v>46209</v>
-      </c>
-      <c r="F28" s="5">
-        <v>46209</v>
-      </c>
-      <c r="G28" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="H28" s="4" t="s">
-        <v>10</v>
-      </c>
+      <c r="A28" s="6"/>
+      <c r="B28" s="3"/>
+      <c r="C28" s="3"/>
+      <c r="D28" s="4"/>
+      <c r="E28" s="5"/>
+      <c r="F28" s="5"/>
+      <c r="G28" s="4"/>
+      <c r="H28" s="4"/>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A29" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="B29" s="3">
-        <v>173365</v>
-      </c>
-      <c r="C29" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D29" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="E29" s="5">
-        <v>46209</v>
-      </c>
-      <c r="F29" s="5">
-        <v>46209</v>
-      </c>
-      <c r="G29" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="H29" s="4" t="s">
-        <v>10</v>
-      </c>
+      <c r="A29" s="6"/>
+      <c r="B29" s="3"/>
+      <c r="C29" s="3"/>
+      <c r="D29" s="4"/>
+      <c r="E29" s="5"/>
+      <c r="F29" s="5"/>
+      <c r="G29" s="4"/>
+      <c r="H29" s="4"/>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A30" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="B30" s="3">
-        <v>173400</v>
-      </c>
-      <c r="C30" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D30" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="E30" s="5">
-        <v>46209</v>
-      </c>
-      <c r="F30" s="5">
-        <v>46209</v>
-      </c>
-      <c r="G30" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="H30" s="4" t="s">
-        <v>10</v>
-      </c>
+      <c r="A30" s="6"/>
+      <c r="B30" s="3"/>
+      <c r="C30" s="3"/>
+      <c r="D30" s="4"/>
+      <c r="E30" s="5"/>
+      <c r="F30" s="5"/>
+      <c r="G30" s="4"/>
+      <c r="H30" s="4"/>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A31" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="B31" s="3">
-        <v>173503</v>
-      </c>
-      <c r="C31" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D31" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="E31" s="5">
-        <v>46209</v>
-      </c>
-      <c r="F31" s="5">
-        <v>46209</v>
-      </c>
-      <c r="G31" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="H31" s="4" t="s">
-        <v>10</v>
-      </c>
+      <c r="A31" s="6"/>
+      <c r="B31" s="3"/>
+      <c r="C31" s="3"/>
+      <c r="D31" s="4"/>
+      <c r="E31" s="5"/>
+      <c r="F31" s="5"/>
+      <c r="G31" s="4"/>
+      <c r="H31" s="4"/>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A32" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="B32" s="3">
-        <v>173344</v>
-      </c>
-      <c r="C32" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D32" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="E32" s="5">
-        <v>46209</v>
-      </c>
-      <c r="F32" s="5">
-        <v>46209</v>
-      </c>
-      <c r="G32" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="H32" s="4" t="s">
-        <v>10</v>
-      </c>
+      <c r="A32" s="6"/>
+      <c r="B32" s="3"/>
+      <c r="C32" s="3"/>
+      <c r="D32" s="4"/>
+      <c r="E32" s="5"/>
+      <c r="F32" s="5"/>
+      <c r="G32" s="4"/>
+      <c r="H32" s="4"/>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A33" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="B33" s="3">
-        <v>173393</v>
-      </c>
-      <c r="C33" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D33" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="E33" s="5">
-        <v>46209</v>
-      </c>
-      <c r="F33" s="5">
-        <v>46209</v>
-      </c>
-      <c r="G33" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="H33" s="4" t="s">
-        <v>10</v>
-      </c>
+      <c r="A33" s="6"/>
+      <c r="B33" s="3"/>
+      <c r="C33" s="3"/>
+      <c r="D33" s="4"/>
+      <c r="E33" s="5"/>
+      <c r="F33" s="5"/>
+      <c r="G33" s="4"/>
+      <c r="H33" s="4"/>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A34" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="B34" s="3">
-        <v>173407</v>
-      </c>
-      <c r="C34" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D34" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="E34" s="5">
-        <v>46209</v>
-      </c>
-      <c r="F34" s="5">
-        <v>46209</v>
-      </c>
-      <c r="G34" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="H34" s="4" t="s">
-        <v>10</v>
-      </c>
+      <c r="A34" s="6"/>
+      <c r="B34" s="3"/>
+      <c r="C34" s="3"/>
+      <c r="D34" s="4"/>
+      <c r="E34" s="5"/>
+      <c r="F34" s="5"/>
+      <c r="G34" s="4"/>
+      <c r="H34" s="4"/>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A35" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="B35" s="3">
-        <v>173434</v>
-      </c>
-      <c r="C35" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D35" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="E35" s="5">
-        <v>46209</v>
-      </c>
-      <c r="F35" s="5">
-        <v>46209</v>
-      </c>
-      <c r="G35" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="H35" s="4" t="s">
-        <v>10</v>
-      </c>
+      <c r="A35" s="6"/>
+      <c r="B35" s="3"/>
+      <c r="C35" s="3"/>
+      <c r="D35" s="4"/>
+      <c r="E35" s="5"/>
+      <c r="F35" s="5"/>
+      <c r="G35" s="4"/>
+      <c r="H35" s="4"/>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A36" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="B36" s="3">
-        <v>176997</v>
-      </c>
-      <c r="C36" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D36" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="E36" s="5">
-        <v>46209</v>
-      </c>
-      <c r="F36" s="5">
-        <v>46209</v>
-      </c>
-      <c r="G36" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="H36" s="4" t="s">
-        <v>10</v>
-      </c>
+      <c r="A36" s="6"/>
+      <c r="B36" s="3"/>
+      <c r="C36" s="3"/>
+      <c r="D36" s="4"/>
+      <c r="E36" s="5"/>
+      <c r="F36" s="5"/>
+      <c r="G36" s="4"/>
+      <c r="H36" s="4"/>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A37" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="B37" s="3">
-        <v>177002</v>
-      </c>
-      <c r="C37" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D37" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="E37" s="5">
-        <v>46209</v>
-      </c>
-      <c r="F37" s="5">
-        <v>46209</v>
-      </c>
-      <c r="G37" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="H37" s="4" t="s">
-        <v>10</v>
-      </c>
+      <c r="A37" s="6"/>
+      <c r="B37" s="3"/>
+      <c r="C37" s="3"/>
+      <c r="D37" s="4"/>
+      <c r="E37" s="5"/>
+      <c r="F37" s="5"/>
+      <c r="G37" s="4"/>
+      <c r="H37" s="4"/>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A38" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="B38" s="3">
-        <v>177039</v>
-      </c>
-      <c r="C38" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D38" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="E38" s="5">
-        <v>46209</v>
-      </c>
-      <c r="F38" s="5">
-        <v>46209</v>
-      </c>
-      <c r="G38" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="H38" s="4" t="s">
-        <v>10</v>
-      </c>
+      <c r="A38" s="6"/>
+      <c r="B38" s="3"/>
+      <c r="C38" s="3"/>
+      <c r="D38" s="4"/>
+      <c r="E38" s="5"/>
+      <c r="F38" s="5"/>
+      <c r="G38" s="4"/>
+      <c r="H38" s="4"/>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A39" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="B39" s="3">
-        <v>177040</v>
-      </c>
-      <c r="C39" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D39" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="E39" s="5">
-        <v>46209</v>
-      </c>
-      <c r="F39" s="5">
-        <v>46209</v>
-      </c>
-      <c r="G39" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="H39" s="4" t="s">
-        <v>10</v>
-      </c>
+      <c r="A39" s="6"/>
+      <c r="B39" s="3"/>
+      <c r="C39" s="3"/>
+      <c r="D39" s="4"/>
+      <c r="E39" s="5"/>
+      <c r="F39" s="5"/>
+      <c r="G39" s="4"/>
+      <c r="H39" s="4"/>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A40" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="B40" s="3">
-        <v>177057</v>
-      </c>
-      <c r="C40" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D40" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="E40" s="5">
-        <v>46209</v>
-      </c>
-      <c r="F40" s="5">
-        <v>46209</v>
-      </c>
-      <c r="G40" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="H40" s="4" t="s">
-        <v>10</v>
-      </c>
+      <c r="A40" s="6"/>
+      <c r="B40" s="3"/>
+      <c r="C40" s="3"/>
+      <c r="D40" s="4"/>
+      <c r="E40" s="5"/>
+      <c r="F40" s="5"/>
+      <c r="G40" s="4"/>
+      <c r="H40" s="4"/>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A41" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="B41" s="3">
-        <v>177071</v>
-      </c>
-      <c r="C41" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D41" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="E41" s="5">
-        <v>46209</v>
-      </c>
-      <c r="F41" s="5">
-        <v>46209</v>
-      </c>
-      <c r="G41" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="H41" s="4" t="s">
-        <v>10</v>
-      </c>
+      <c r="A41" s="6"/>
+      <c r="B41" s="3"/>
+      <c r="C41" s="3"/>
+      <c r="D41" s="4"/>
+      <c r="E41" s="5"/>
+      <c r="F41" s="5"/>
+      <c r="G41" s="4"/>
+      <c r="H41" s="4"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:B1">
